--- a/data/trans_orig/KP10in_T-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/KP10in_T-Estudios-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN percibido por tutor (escala)</t>
+          <t>KIDSCREEN percibido por tutor (escala) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>61,95; 71,48</t>
+          <t>62,12; 72,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57,31; 64,43</t>
+          <t>57,11; 64,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60,82; 67,28</t>
+          <t>60,92; 67,21</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61,36; 66,81</t>
+          <t>60,71; 66,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,24; 65,09</t>
+          <t>61,22; 65,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62,04; 65,43</t>
+          <t>62,06; 65,37</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64,62; 69,58</t>
+          <t>64,65; 69,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66,06; 71,8</t>
+          <t>65,8; 71,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,27; 70,24</t>
+          <t>66,22; 70,06</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>62,53; 66,91</t>
+          <t>62,67; 66,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62,82; 66,11</t>
+          <t>62,74; 66,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,48; 66,02</t>
+          <t>63,26; 66,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KP10in_T-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/KP10in_T-Estudios-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN percibido por tutor (escala) (tasa de respuesta: 100,0%)</t>
+          <t>KIDSCREEN percibido por adulto (escala) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>62,12; 72,08</t>
+          <t>61,95; 71,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57,11; 64,42</t>
+          <t>57,01; 64,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60,92; 67,21</t>
+          <t>60,89; 67,04</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>60,71; 66,69</t>
+          <t>60,81; 66,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,22; 65,23</t>
+          <t>61,27; 65,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62,06; 65,37</t>
+          <t>62,01; 65,37</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64,65; 69,73</t>
+          <t>64,5; 69,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65,8; 71,96</t>
+          <t>66,01; 71,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,22; 70,06</t>
+          <t>66,08; 70,08</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>62,67; 66,91</t>
+          <t>62,34; 66,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62,74; 66,11</t>
+          <t>62,85; 66,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,26; 66,08</t>
+          <t>63,3; 66,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KP10in_T-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/KP10in_T-Estudios-trans_orig.xlsx
@@ -489,18 +489,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN percibido por adulto (escala) (tasa de respuesta: 100,0%)</t>
+          <t>KIDSCREEN percibido por adulto/a (escala) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>66,4</t>
+          <t>60,26</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>60,48</t>
+          <t>65,92</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63,66</t>
+          <t>63,18</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>61,95; 71,49</t>
+          <t>57,04; 64,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57,01; 64,1</t>
+          <t>61,35; 71,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60,89; 67,04</t>
+          <t>60,47; 66,9</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>64,66</t>
+          <t>63,8</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>63,44</t>
+          <t>65,99</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63,99</t>
+          <t>64,78</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>60,81; 66,69</t>
+          <t>62,18; 65,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,27; 65,16</t>
+          <t>64,45; 67,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62,01; 65,37</t>
+          <t>63,65; 65,98</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>67,17</t>
+          <t>69,58</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>68,99</t>
+          <t>67,23</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68,19</t>
+          <t>68,48</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64,5; 69,53</t>
+          <t>66,83; 72,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66,01; 71,71</t>
+          <t>64,67; 69,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,08; 70,08</t>
+          <t>66,67; 70,32</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>65,35</t>
+          <t>64,93</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>64,57</t>
+          <t>66,28</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64,93</t>
+          <t>65,55</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>62,34; 66,79</t>
+          <t>63,64; 66,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62,85; 66,07</t>
+          <t>65,07; 67,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,3; 66,01</t>
+          <t>64,65; 66,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KP10in_T-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/KP10in_T-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -97,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -110,6 +112,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -489,7 +494,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN percibido por adulto/a (escala) (tasa de respuesta: 100,0%)</t>
+          <t>KIDSCREEN percibido por adulto/a (escala) (tasa de respuesta: 49,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -546,149 +551,109 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>60,26</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>65,92</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>63,18</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>60.26343923756789</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>65.9232753399552</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>63.18301163295315</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>57,04; 64,29</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>61,35; 71,32</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>60,47; 66,9</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>57.04390000142288</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>61.3472551355876</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>60.46750086894162</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>64.28871113427242</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>71.31772898155535</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>66.90235741017436</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>63,8</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>65,99</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>64,78</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>62,18; 65,28</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>64,45; 67,62</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>63,65; 65,98</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>63.79817764509075</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>65.98788469846801</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>64.78496445359819</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>69,58</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>67,23</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>68,48</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>62.17903722112584</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>64.44975443173915</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>63.65479360176767</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>66,83; 72,32</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>64,67; 69,66</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>66,67; 70,32</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>65.27910255492139</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>67.61548483945668</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>65.98465250741319</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -696,47 +661,107 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>64,93</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>66,28</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>65,55</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>69.5814420342016</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>67.23054750299085</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>68.48130654058814</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>63,64; 66,39</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>65,07; 67,66</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>64,65; 66,49</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>66.82937697483185</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>64.66596634982349</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>66.67435694909312</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>72.32431856077866</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>69.65907912437044</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>70.31724296913497</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>64.92732094460014</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>66.28067204261059</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>65.54846297643974</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>63.64034898981852</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>65.06789259723863</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>64.65044445765709</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>66.38548833554718</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>67.65564031366436</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>66.48919769510343</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -744,11 +769,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
